--- a/result/train_info_group_part_detrend_plr_stft_bin_win_anova.xlsx
+++ b/result/train_info_group_part_detrend_plr_stft_bin_win_anova.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
@@ -467,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.105456352233887</v>
+        <v>4.605304956436157</v>
       </c>
       <c r="C2" t="n">
         <v>0.9404940119760479</v>
@@ -489,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.57979106903076</v>
+        <v>20.64391183853149</v>
       </c>
       <c r="C3" t="n">
         <v>0.9925871015567087</v>
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03709268569946289</v>
+        <v>0.01399922370910645</v>
       </c>
       <c r="C4" t="n">
         <v>0.997039230199852</v>
@@ -533,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.333396673202515</v>
+        <v>1.566926002502441</v>
       </c>
       <c r="C5" t="n">
-        <v>0.799552071668533</v>
+        <v>0.8002991772625281</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7939214232765011</v>
+        <v>0.793180133432172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7967267993304816</v>
+        <v>0.7967237527922562</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7969156447417317</v>
+        <v>0.7971014492753623</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +543,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.80427479743958</v>
+        <v>118.5597035884857</v>
       </c>
       <c r="C6" t="n">
         <v>0.9592061742006616</v>
